--- a/Data/FlightPlan/FPL_22OCT26.xlsx
+++ b/Data/FlightPlan/FPL_22OCT26.xlsx
@@ -161,516 +161,519 @@
     <t>13:55</t>
   </si>
   <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>VN-A203</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>TXN</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A521</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>08:13</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A528</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
     <t>10:10</t>
   </si>
   <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>17:25</t>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>PUS</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>19:10</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>13:50</t>
   </si>
   <si>
     <t>15:35</t>
   </si>
   <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>VN-A203</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>TXN</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A521</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>DAD</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A528</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>PUS</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>19:10</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
     <t>VDH</t>
   </si>
   <si>
@@ -746,6 +749,9 @@
     <t>VN-A629</t>
   </si>
   <si>
+    <t>11:50</t>
+  </si>
+  <si>
     <t>21:25</t>
   </si>
   <si>
@@ -1163,7 +1169,7 @@
     <t>Total Record(s): 331</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 21, 2026 21:39</t>
+    <t xml:space="preserve">Generated on  Oct 22, 2026 03:53</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2137,17 +2143,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I20" s="7">
+        <v>51</v>
+      </c>
+      <c t="s" r="J20" s="7">
         <v>52</v>
       </c>
-      <c t="s" r="J20" s="7">
+      <c t="s" r="K20" s="7">
         <v>53</v>
-      </c>
-      <c t="s" r="K20" s="7">
-        <v>54</v>
       </c>
       <c r="L20" s="7"/>
       <c t="s" r="M20" s="7">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
@@ -2171,13 +2177,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H21" s="8">
+        <v>55</v>
+      </c>
+      <c t="s" r="I21" s="7">
         <v>56</v>
       </c>
-      <c t="s" r="I21" s="7">
+      <c t="s" r="J21" s="7">
         <v>57</v>
-      </c>
-      <c t="s" r="J21" s="7">
-        <v>58</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -2210,7 +2216,7 @@
       </c>
       <c r="D23" s="7"/>
       <c t="s" r="E23" s="7">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F23" s="7">
         <v>321</v>
@@ -2222,10 +2228,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I23" s="7">
+        <v>59</v>
+      </c>
+      <c t="s" r="J23" s="7">
         <v>60</v>
-      </c>
-      <c t="s" r="J23" s="7">
-        <v>61</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -2243,7 +2249,7 @@
       </c>
       <c r="D24" s="7"/>
       <c t="s" r="E24" s="7">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F24" s="7">
         <v>321</v>
@@ -2255,7 +2261,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c t="s" r="J24" s="7">
         <v>33</v>
@@ -2276,7 +2282,7 @@
       </c>
       <c r="D25" s="7"/>
       <c t="s" r="E25" s="7">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F25" s="7">
         <v>321</v>
@@ -2285,13 +2291,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H25" s="8">
+        <v>62</v>
+      </c>
+      <c t="s" r="I25" s="7">
         <v>63</v>
       </c>
-      <c t="s" r="I25" s="7">
+      <c t="s" r="J25" s="7">
         <v>64</v>
-      </c>
-      <c t="s" r="J25" s="7">
-        <v>65</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2309,22 +2315,22 @@
       </c>
       <c r="D26" s="7"/>
       <c t="s" r="E26" s="7">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F26" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G26" s="8">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c t="s" r="H26" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I26" s="7">
+        <v>65</v>
+      </c>
+      <c t="s" r="J26" s="7">
         <v>66</v>
-      </c>
-      <c t="s" r="J26" s="7">
-        <v>67</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2342,7 +2348,7 @@
       </c>
       <c r="D27" s="7"/>
       <c t="s" r="E27" s="7">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F27" s="7">
         <v>321</v>
@@ -2357,7 +2363,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2390,7 +2396,7 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
@@ -2402,14 +2408,16 @@
         <v>20</v>
       </c>
       <c t="s" r="I29" s="7">
+        <v>69</v>
+      </c>
+      <c t="s" r="J29" s="7">
         <v>70</v>
-      </c>
-      <c t="s" r="J29" s="7">
-        <v>71</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
+      <c t="s" r="M29" s="7">
+        <v>71</v>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c t="s" r="A30" s="6">
@@ -2423,7 +2431,7 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -2456,7 +2464,7 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
@@ -2489,7 +2497,7 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
@@ -2795,10 +2803,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2825,13 +2833,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="I43" s="7">
         <v>89</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2855,16 +2863,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2897,7 +2905,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -2909,10 +2917,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2930,7 +2938,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -2939,13 +2947,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -2963,19 +2971,19 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="H48" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c t="s" r="J48" s="7">
         <v>108</v>
@@ -3056,10 +3064,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3086,13 +3094,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="I52" s="7">
         <v>74</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3116,7 +3124,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>16</v>
@@ -3125,7 +3133,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3152,13 +3160,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3182,16 +3190,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3224,7 +3232,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3233,10 +3241,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J57" s="7">
         <v>82</v>
@@ -3257,22 +3265,22 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3290,19 +3298,19 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J59" s="7">
         <v>21</v>
@@ -3323,13 +3331,13 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>47</v>
@@ -3338,7 +3346,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3356,7 +3364,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3365,10 +3373,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c t="s" r="J61" s="7">
         <v>128</v>
@@ -3389,13 +3397,13 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>47</v>
@@ -3518,7 +3526,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3548,10 +3556,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I67" s="7">
+        <v>137</v>
+      </c>
+      <c t="s" r="J67" s="7">
         <v>138</v>
-      </c>
-      <c t="s" r="J67" s="7">
-        <v>139</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3584,19 +3592,19 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
+        <v>139</v>
+      </c>
+      <c r="F69" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G69" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H69" s="8">
         <v>140</v>
       </c>
-      <c r="F69" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G69" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H69" s="8">
+      <c t="s" r="I69" s="7">
         <v>141</v>
-      </c>
-      <c t="s" r="I69" s="7">
-        <v>142</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>82</v>
@@ -3617,22 +3625,22 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
+        <v>139</v>
+      </c>
+      <c r="F70" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G70" s="8">
         <v>140</v>
       </c>
-      <c r="F70" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G70" s="8">
-        <v>141</v>
-      </c>
       <c t="s" r="H70" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3650,19 +3658,19 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
+        <v>139</v>
+      </c>
+      <c r="F71" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G71" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H71" s="8">
         <v>140</v>
       </c>
-      <c r="F71" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G71" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H71" s="8">
-        <v>141</v>
-      </c>
       <c t="s" r="I71" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="J71" s="7">
         <v>136</v>
@@ -3683,22 +3691,22 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
+        <v>139</v>
+      </c>
+      <c r="F72" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G72" s="8">
         <v>140</v>
       </c>
-      <c r="F72" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G72" s="8">
-        <v>141</v>
-      </c>
       <c t="s" r="H72" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I72" s="7">
+        <v>144</v>
+      </c>
+      <c t="s" r="J72" s="7">
         <v>145</v>
-      </c>
-      <c t="s" r="J72" s="7">
-        <v>55</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3716,7 +3724,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3725,7 +3733,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="I73" s="7">
         <v>146</v>
@@ -3749,13 +3757,13 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>16</v>
@@ -3806,13 +3814,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="I76" s="7">
         <v>151</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3836,7 +3844,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>152</v>
@@ -3872,7 +3880,7 @@
         <v>152</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="I78" s="7">
         <v>154</v>
@@ -3902,7 +3910,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>16</v>
@@ -3944,7 +3952,7 @@
         <v>49</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -3977,7 +3985,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4062,7 +4070,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4122,13 +4130,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4152,7 +4160,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>47</v>
@@ -4161,7 +4169,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4194,7 +4202,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4224,10 +4232,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4407,7 +4415,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4437,7 +4445,7 @@
         <v>176</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>177</v>
@@ -4515,7 +4523,7 @@
         <v>80</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="I99" s="7">
         <v>180</v>
@@ -4545,7 +4553,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>80</v>
@@ -4587,7 +4595,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4698,10 +4706,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4734,7 +4742,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4779,7 +4787,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>189</v>
@@ -4878,10 +4886,10 @@
         <v>80</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5121,7 +5129,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="I119" s="7">
         <v>192</v>
@@ -5151,7 +5159,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>47</v>
@@ -5160,7 +5168,7 @@
         <v>201</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5274,7 +5282,7 @@
         <v>207</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5301,7 +5309,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I125" s="7">
         <v>201</v>
@@ -5335,7 +5343,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>16</v>
@@ -5398,9 +5406,13 @@
       <c t="s" r="J128" s="7">
         <v>95</v>
       </c>
-      <c r="K128" s="7"/>
+      <c t="s" r="K128" s="7">
+        <v>81</v>
+      </c>
       <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
+      <c t="s" r="M128" s="7">
+        <v>33</v>
+      </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
       <c t="s" r="A129" s="6">
@@ -5429,7 +5441,7 @@
         <v>214</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5459,10 +5471,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5576,7 +5588,7 @@
         <v>197</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5603,7 +5615,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I135" s="7">
         <v>218</v>
@@ -5633,7 +5645,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>16</v>
@@ -5672,10 +5684,10 @@
         <v>165</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>54</v>
+        <v>220</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5735,13 +5747,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="I139" s="7">
         <v>129</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5765,7 +5777,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>16</v>
@@ -5774,7 +5786,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5807,7 +5819,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5840,7 +5852,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5855,7 +5867,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5873,7 +5885,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5882,7 +5894,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I144" s="7">
         <v>43</v>
@@ -5921,7 +5933,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5933,10 +5945,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5954,7 +5966,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -5969,7 +5981,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -5987,7 +5999,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6002,7 +6014,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6020,7 +6032,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6032,7 +6044,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>182</v>
@@ -6053,7 +6065,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6065,10 +6077,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6086,7 +6098,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6098,7 +6110,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>38</v>
@@ -6119,7 +6131,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6152,7 +6164,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6200,7 +6212,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6209,13 +6221,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I155" s="7">
         <v>213</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6233,13 +6245,13 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>47</v>
@@ -6266,7 +6278,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6278,10 +6290,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6299,7 +6311,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6311,10 +6323,10 @@
         <v>156</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6332,7 +6344,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6380,7 +6392,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6389,7 +6401,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="I161" s="7">
         <v>81</v>
@@ -6413,13 +6425,13 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>16</v>
@@ -6428,7 +6440,7 @@
         <v>191</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6446,7 +6458,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6455,7 +6467,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="I163" s="7">
         <v>183</v>
@@ -6479,22 +6491,22 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6527,7 +6539,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6539,14 +6551,18 @@
         <v>16</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>164</v>
       </c>
-      <c r="K166" s="7"/>
+      <c t="s" r="K166" s="7">
+        <v>236</v>
+      </c>
       <c r="L166" s="7"/>
-      <c r="M166" s="7"/>
+      <c t="s" r="M166" s="7">
+        <v>246</v>
+      </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c t="s" r="A167" s="6">
@@ -6560,7 +6576,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6593,7 +6609,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6608,7 +6624,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6626,7 +6642,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6635,13 +6651,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6659,22 +6675,22 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6707,7 +6723,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6716,10 +6732,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>34</v>
@@ -6740,13 +6756,13 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>47</v>
@@ -6773,7 +6789,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6788,7 +6804,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="K174" s="7">
         <v>160</v>
@@ -6810,7 +6826,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6825,7 +6841,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6858,7 +6874,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6870,10 +6886,10 @@
         <v>165</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6891,7 +6907,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6903,10 +6919,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6924,7 +6940,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6933,7 +6949,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="I179" s="7">
         <v>133</v>
@@ -6957,13 +6973,13 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>47</v>
@@ -6990,7 +7006,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7023,7 +7039,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7038,7 +7054,7 @@
         <v>202</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7056,7 +7072,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7065,13 +7081,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7089,22 +7105,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7137,7 +7153,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7149,10 +7165,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7170,7 +7186,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7179,13 +7195,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="I187" s="7">
         <v>219</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7203,13 +7219,13 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>47</v>
@@ -7218,7 +7234,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7251,7 +7267,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7263,7 +7279,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>189</v>
@@ -7284,7 +7300,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7296,10 +7312,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7317,7 +7333,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7332,7 +7348,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7350,7 +7366,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7362,10 +7378,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7383,7 +7399,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7398,7 +7414,7 @@
         <v>202</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7416,7 +7432,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7431,7 +7447,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7464,7 +7480,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7476,10 +7492,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7497,7 +7513,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7512,7 +7528,7 @@
         <v>192</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7530,7 +7546,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7542,10 +7558,10 @@
         <v>156</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7563,7 +7579,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7575,10 +7591,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7611,7 +7627,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7623,7 +7639,7 @@
         <v>152</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>81</v>
@@ -7644,7 +7660,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7656,7 +7672,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>18</v>
@@ -7677,7 +7693,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7689,10 +7705,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7710,7 +7726,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7725,7 +7741,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7743,7 +7759,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7776,7 +7792,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7791,7 +7807,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7809,7 +7825,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7821,10 +7837,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7842,7 +7858,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7854,10 +7870,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7890,7 +7906,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7899,13 +7915,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="I211" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7923,13 +7939,13 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>16</v>
@@ -7938,7 +7954,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7956,7 +7972,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7968,7 +7984,7 @@
         <v>80</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="J213" s="7">
         <v>183</v>
@@ -7989,7 +8005,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8001,7 +8017,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>24</v>
@@ -8022,7 +8038,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8037,7 +8053,7 @@
         <v>210</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8070,7 +8086,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8079,13 +8095,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="I217" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8103,13 +8119,13 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>16</v>
@@ -8136,7 +8152,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8148,13 +8164,13 @@
         <v>47</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="K219" s="7">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
@@ -8188,7 +8204,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8200,7 +8216,7 @@
         <v>156</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>81</v>
@@ -8221,7 +8237,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8233,10 +8249,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8254,7 +8270,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8266,10 +8282,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8287,7 +8303,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8320,7 +8336,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8332,13 +8348,13 @@
         <v>47</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>183</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
@@ -8357,7 +8373,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8369,13 +8385,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>210</v>
       </c>
       <c t="s" r="K226" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
@@ -8394,7 +8410,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8403,16 +8419,16 @@
         <v>16</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="K227" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
@@ -8431,29 +8447,29 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>184</v>
       </c>
       <c t="s" r="K228" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -8483,7 +8499,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8495,7 +8511,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>155</v>
@@ -8516,7 +8532,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8531,7 +8547,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8549,7 +8565,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8564,14 +8580,14 @@
         <v>164</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="K232" s="7">
         <v>21</v>
       </c>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -8586,7 +8602,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8601,7 +8617,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8619,7 +8635,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8631,10 +8647,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8667,7 +8683,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8700,7 +8716,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8709,10 +8725,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>37</v>
@@ -8733,13 +8749,13 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>47</v>
@@ -8766,7 +8782,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8781,7 +8797,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8814,22 +8830,22 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8847,7 +8863,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8856,7 +8872,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>192</v>
@@ -8880,13 +8896,13 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>16</v>
@@ -8895,7 +8911,7 @@
         <v>201</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8913,7 +8929,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8922,13 +8938,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8961,7 +8977,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -8994,7 +9010,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9016,7 +9032,7 @@
       </c>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9046,7 +9062,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9079,7 +9095,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9112,7 +9128,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9124,7 +9140,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>49</v>
@@ -9145,7 +9161,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9157,7 +9173,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>86</v>
@@ -9178,7 +9194,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9190,10 +9206,10 @@
         <v>152</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9211,7 +9227,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9244,7 +9260,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9253,13 +9269,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9292,7 +9308,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9304,10 +9320,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9325,7 +9341,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9334,13 +9350,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I258" s="7">
         <v>180</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9358,13 +9374,13 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>47</v>
@@ -9373,7 +9389,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9391,7 +9407,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9400,10 +9416,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>37</v>
@@ -9424,13 +9440,13 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>47</v>
@@ -9439,7 +9455,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9472,7 +9488,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9487,7 +9503,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9505,7 +9521,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9520,7 +9536,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9538,7 +9554,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9547,13 +9563,13 @@
         <v>156</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9571,13 +9587,13 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>156</v>
@@ -9586,7 +9602,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9604,7 +9620,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9637,7 +9653,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9649,10 +9665,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9685,22 +9701,22 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9718,7 +9734,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9727,13 +9743,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="I271" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9751,22 +9767,22 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9784,7 +9800,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9793,13 +9809,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9832,7 +9848,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9841,10 +9857,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>213</v>
@@ -9865,22 +9881,22 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9898,7 +9914,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -9907,7 +9923,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>82</v>
@@ -9931,13 +9947,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>16</v>
@@ -9946,7 +9962,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9964,7 +9980,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -9979,7 +9995,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9997,7 +10013,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10012,10 +10028,10 @@
         <v>74</v>
       </c>
       <c t="s" r="J280" s="7">
+        <v>97</v>
+      </c>
+      <c t="s" r="K280" s="7">
         <v>51</v>
-      </c>
-      <c t="s" r="K280" s="7">
-        <v>52</v>
       </c>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
@@ -10034,7 +10050,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10046,10 +10062,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10082,7 +10098,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10091,13 +10107,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10115,22 +10131,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10148,7 +10164,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10163,7 +10179,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10181,7 +10197,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10193,10 +10209,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10214,7 +10230,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10223,13 +10239,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="I287" s="7">
         <v>136</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10247,13 +10263,13 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>47</v>
@@ -10262,7 +10278,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10295,13 +10311,13 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>47</v>
@@ -10328,7 +10344,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10340,7 +10356,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>36</v>
@@ -10361,7 +10377,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10394,7 +10410,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10406,10 +10422,10 @@
         <v>80</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10442,7 +10458,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -10475,7 +10491,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -10484,13 +10500,13 @@
         <v>165</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10508,19 +10524,19 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>165</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>91</v>
@@ -10541,7 +10557,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10553,10 +10569,10 @@
         <v>131</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10589,7 +10605,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10598,13 +10614,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>190</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10622,13 +10638,13 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>16</v>
@@ -10637,7 +10653,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10655,7 +10671,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -10664,7 +10680,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="I302" s="7">
         <v>175</v>
@@ -10688,13 +10704,13 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>16</v>
@@ -10736,7 +10752,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10748,10 +10764,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10769,7 +10785,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -10802,7 +10818,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10835,7 +10851,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -10847,10 +10863,10 @@
         <v>80</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10868,7 +10884,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -10877,13 +10893,13 @@
         <v>80</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10901,22 +10917,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>80</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10934,7 +10950,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -10982,7 +10998,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -10991,13 +11007,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11015,19 +11031,19 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>214</v>
@@ -11048,7 +11064,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11060,7 +11076,7 @@
         <v>156</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>34</v>
@@ -11081,7 +11097,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11114,7 +11130,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11123,13 +11139,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="I317" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11147,13 +11163,13 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>16</v>
@@ -11195,7 +11211,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11228,7 +11244,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11237,13 +11253,13 @@
         <v>80</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11261,13 +11277,13 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>80</v>
@@ -11294,7 +11310,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11306,10 +11322,10 @@
         <v>131</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11342,7 +11358,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11351,13 +11367,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11375,19 +11391,19 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>76</v>
@@ -11408,7 +11424,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11441,7 +11457,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11453,10 +11469,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11489,7 +11505,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11501,17 +11517,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>199</v>
       </c>
       <c t="s" r="K330" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -11526,7 +11542,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11538,13 +11554,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>36</v>
       </c>
       <c t="s" r="K331" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
@@ -11563,7 +11579,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11578,7 +11594,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11596,7 +11612,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11611,7 +11627,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11629,7 +11645,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11641,10 +11657,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11662,7 +11678,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11674,10 +11690,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11710,7 +11726,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11722,7 +11738,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>180</v>
@@ -11743,7 +11759,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11752,10 +11768,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>75</v>
@@ -11776,19 +11792,19 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>175</v>
@@ -11809,7 +11825,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11818,10 +11834,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>89</v>
@@ -11842,13 +11858,13 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>16</v>
@@ -11857,7 +11873,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11890,7 +11906,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11899,13 +11915,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11923,13 +11939,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>47</v>
@@ -11938,7 +11954,7 @@
         <v>199</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11956,7 +11972,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -11965,10 +11981,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>185</v>
@@ -11989,22 +12005,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12037,7 +12053,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
@@ -12046,13 +12062,13 @@
         <v>80</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12070,13 +12086,13 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>80</v>
@@ -12085,7 +12101,7 @@
         <v>200</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12103,7 +12119,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12112,7 +12128,7 @@
         <v>80</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>77</v>
@@ -12136,19 +12152,19 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>80</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>204</v>
@@ -12169,7 +12185,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12181,10 +12197,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12217,19 +12233,19 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>181</v>
@@ -12250,7 +12266,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12262,7 +12278,7 @@
         <v>80</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>199</v>
@@ -12283,7 +12299,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12298,7 +12314,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12316,7 +12332,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12328,7 +12344,7 @@
         <v>165</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>37</v>
@@ -12349,7 +12365,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12364,7 +12380,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12382,7 +12398,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12394,7 +12410,7 @@
         <v>131</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>197</v>
@@ -12430,7 +12446,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12442,7 +12458,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>18</v>
@@ -12463,7 +12479,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12478,7 +12494,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12496,7 +12512,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12508,7 +12524,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>85</v>
@@ -12529,7 +12545,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12541,7 +12557,7 @@
         <v>80</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>160</v>
@@ -12562,7 +12578,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12571,13 +12587,13 @@
         <v>80</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12595,22 +12611,22 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>80</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12643,7 +12659,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12676,7 +12692,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12688,7 +12704,7 @@
         <v>80</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>166</v>
@@ -12709,7 +12725,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12742,7 +12758,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12775,7 +12791,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12784,13 +12800,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12808,22 +12824,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12856,7 +12872,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12865,13 +12881,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>73</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12889,19 +12905,19 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>34</v>
@@ -12922,7 +12938,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -12931,10 +12947,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>174</v>
@@ -12955,19 +12971,19 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>76</v>
@@ -12988,7 +13004,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -12997,10 +13013,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>178</v>
@@ -13021,19 +13037,19 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>151</v>
@@ -13069,13 +13085,13 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>47</v>
@@ -13102,7 +13118,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13114,7 +13130,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>193</v>
@@ -13135,7 +13151,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13179,11 +13195,11 @@
         <v>664</v>
       </c>
       <c t="s" r="C386" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F386" s="7">
         <v>330</v>
@@ -13198,7 +13214,7 @@
         <v>183</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13216,7 +13232,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F387" s="7">
         <v>330</v>
@@ -13225,13 +13241,13 @@
         <v>165</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13249,29 +13265,29 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F388" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>165</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c t="s" r="K388" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -13301,7 +13317,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F390" s="7">
         <v>330</v>
@@ -13310,7 +13326,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="I390" s="7">
         <v>214</v>
@@ -13334,19 +13350,19 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F391" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>151</v>
@@ -13382,7 +13398,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
@@ -13391,13 +13407,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>133</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13415,22 +13431,22 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F394" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13463,7 +13479,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
@@ -13496,7 +13512,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
@@ -13505,7 +13521,7 @@
         <v>165</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c t="s" r="I397" s="7">
         <v>21</v>
@@ -13529,19 +13545,19 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>165</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>213</v>
@@ -13577,7 +13593,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
@@ -13586,13 +13602,13 @@
         <v>165</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13610,19 +13626,19 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>165</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>216</v>
@@ -13658,19 +13674,19 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>175</v>
@@ -13691,7 +13707,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -13700,13 +13716,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13714,7 +13730,7 @@
     </row>
     <row r="405" ht="16.5" customHeight="1">
       <c t="s" r="A405" s="9">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B405" s="9"/>
       <c r="C405" s="9"/>
@@ -13734,7 +13750,7 @@
     <row r="406" ht="65.25" customHeight="1"/>
     <row r="407" ht="16.5" customHeight="1">
       <c t="s" r="A407" s="10">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B407" s="10"/>
       <c r="C407" s="10"/>
@@ -13747,7 +13763,7 @@
       <c r="J407" s="10"/>
       <c r="K407" s="10"/>
       <c t="s" r="L407" s="11">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M407" s="11"/>
       <c r="N407" s="11"/>

--- a/Data/FlightPlan/FPL_22OCT26.xlsx
+++ b/Data/FlightPlan/FPL_22OCT26.xlsx
@@ -194,6 +194,9 @@
     <t>07:50</t>
   </si>
   <si>
+    <t>07:47</t>
+  </si>
+  <si>
     <t>08:20</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
     <t>07:35</t>
   </si>
   <si>
-    <t>08:13</t>
-  </si>
-  <si>
     <t>TPE</t>
   </si>
   <si>
@@ -314,6 +314,12 @@
     <t>07:40</t>
   </si>
   <si>
+    <t>07:38</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
     <t>VII</t>
   </si>
   <si>
@@ -326,255 +332,279 @@
     <t>12:25</t>
   </si>
   <si>
-    <t>VN-A529</t>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>PUS</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:37</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>07:10</t>
   </si>
   <si>
     <t>07:30</t>
   </si>
   <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
     <t>10:10</t>
   </si>
   <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>PUS</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:37</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>DAD</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>20:45</t>
   </si>
   <si>
     <t>21:15</t>
   </si>
   <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
     <t>VN-A549</t>
   </si>
   <si>
@@ -602,13 +632,7 @@
     <t>VN-A551</t>
   </si>
   <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>07:04</t>
-  </si>
-  <si>
-    <t>10:50</t>
+    <t>07:12</t>
   </si>
   <si>
     <t>13:30</t>
@@ -623,9 +647,6 @@
     <t>19:20</t>
   </si>
   <si>
-    <t>21:30</t>
-  </si>
-  <si>
     <t>22:40</t>
   </si>
   <si>
@@ -656,9 +677,6 @@
     <t>06:45</t>
   </si>
   <si>
-    <t>10:15</t>
-  </si>
-  <si>
     <t>VVO</t>
   </si>
   <si>
@@ -701,6 +719,9 @@
     <t>06:00</t>
   </si>
   <si>
+    <t>08:16</t>
+  </si>
+  <si>
     <t>09:55</t>
   </si>
   <si>
@@ -752,7 +773,7 @@
     <t>VN-A629</t>
   </si>
   <si>
-    <t>11:50</t>
+    <t>12:49</t>
   </si>
   <si>
     <t>21:25</t>
@@ -791,7 +812,7 @@
     <t>05:45</t>
   </si>
   <si>
-    <t>08:05</t>
+    <t>07:46</t>
   </si>
   <si>
     <t>CAN</t>
@@ -830,9 +851,6 @@
     <t>07:55</t>
   </si>
   <si>
-    <t>12:55</t>
-  </si>
-  <si>
     <t>23:55</t>
   </si>
   <si>
@@ -845,6 +863,9 @@
     <t>06:30</t>
   </si>
   <si>
+    <t>07:24</t>
+  </si>
+  <si>
     <t>10:00</t>
   </si>
   <si>
@@ -854,9 +875,6 @@
     <t>15:05</t>
   </si>
   <si>
-    <t>20:45</t>
-  </si>
-  <si>
     <t>22:05</t>
   </si>
   <si>
@@ -893,6 +911,9 @@
     <t>VN-A642</t>
   </si>
   <si>
+    <t>07:36</t>
+  </si>
+  <si>
     <t>21:05</t>
   </si>
   <si>
@@ -920,9 +941,6 @@
     <t>VN-A647</t>
   </si>
   <si>
-    <t>10:14</t>
-  </si>
-  <si>
     <t>23:20</t>
   </si>
   <si>
@@ -971,6 +989,9 @@
     <t>VN-A656</t>
   </si>
   <si>
+    <t>06:53</t>
+  </si>
+  <si>
     <t>VN-A657</t>
   </si>
   <si>
@@ -1013,6 +1034,9 @@
     <t>VN-A667</t>
   </si>
   <si>
+    <t>06:49</t>
+  </si>
+  <si>
     <t>13:20</t>
   </si>
   <si>
@@ -1025,6 +1049,9 @@
     <t>06:35</t>
   </si>
   <si>
+    <t>08:15</t>
+  </si>
+  <si>
     <t>CMB</t>
   </si>
   <si>
@@ -1073,6 +1100,9 @@
     <t>HIJ</t>
   </si>
   <si>
+    <t>12:23</t>
+  </si>
+  <si>
     <t>PKX</t>
   </si>
   <si>
@@ -1097,6 +1127,9 @@
     <t>VN-A683</t>
   </si>
   <si>
+    <t>12:27</t>
+  </si>
+  <si>
     <t>01:05</t>
   </si>
   <si>
@@ -1181,7 +1214,7 @@
     <t>Total Record(s): 331</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 22, 2026 05:23</t>
+    <t xml:space="preserve">Generated on  Oct 22, 2026 07:11</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2247,7 +2280,9 @@
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
+      <c t="s" r="M23" s="7">
+        <v>61</v>
+      </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c t="s" r="A24" s="6">
@@ -2273,7 +2308,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J24" s="7">
         <v>33</v>
@@ -2303,13 +2338,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H25" s="8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="I25" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J25" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2333,16 +2368,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G26" s="8">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="H26" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -2375,7 +2410,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -2408,7 +2443,7 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
@@ -2420,10 +2455,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -2443,7 +2478,7 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -2476,7 +2511,7 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
@@ -2509,7 +2544,7 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
@@ -2870,37 +2905,21 @@
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
+      <c t="s" r="M44" s="7">
+        <v>101</v>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c t="s" r="A45" s="6">
-        <v>13</v>
-      </c>
-      <c r="B45" s="7">
-        <v>212</v>
-      </c>
-      <c t="s" r="C45" s="7">
-        <v>14</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
       <c r="D45" s="7"/>
-      <c t="s" r="E45" s="7">
-        <v>98</v>
-      </c>
-      <c r="F45" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G45" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H45" s="8">
-        <v>101</v>
-      </c>
-      <c t="s" r="I45" s="7">
-        <v>102</v>
-      </c>
-      <c t="s" r="J45" s="7">
-        <v>103</v>
-      </c>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c r="M45" s="7"/>
@@ -2910,45 +2929,63 @@
         <v>13</v>
       </c>
       <c r="B46" s="7">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c t="s" r="C46" s="7">
         <v>14</v>
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
+      <c t="s" r="A47" s="6">
+        <v>13</v>
+      </c>
+      <c r="B47" s="7">
+        <v>215</v>
+      </c>
+      <c t="s" r="C47" s="7">
+        <v>14</v>
+      </c>
       <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
+      <c t="s" r="E47" s="7">
+        <v>102</v>
+      </c>
+      <c r="F47" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G47" s="8">
+        <v>103</v>
+      </c>
+      <c t="s" r="H47" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I47" s="7">
+        <v>50</v>
+      </c>
+      <c t="s" r="J47" s="7">
+        <v>106</v>
+      </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
@@ -2958,14 +2995,14 @@
         <v>13</v>
       </c>
       <c r="B48" s="7">
-        <v>126</v>
+        <v>807</v>
       </c>
       <c t="s" r="C48" s="7">
         <v>14</v>
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -2974,13 +3011,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -2991,29 +3028,29 @@
         <v>13</v>
       </c>
       <c r="B49" s="7">
-        <v>131</v>
+        <v>800</v>
       </c>
       <c t="s" r="C49" s="7">
         <v>14</v>
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3024,14 +3061,14 @@
         <v>13</v>
       </c>
       <c r="B50" s="7">
-        <v>807</v>
+        <v>883</v>
       </c>
       <c t="s" r="C50" s="7">
         <v>14</v>
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3040,13 +3077,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3054,114 +3091,114 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c t="s" r="A51" s="6">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B51" s="7">
-        <v>800</v>
+        <v>884</v>
       </c>
       <c t="s" r="C51" s="7">
         <v>14</v>
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="H51" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c r="M51" s="7"/>
     </row>
     <row r="52" ht="14.25" customHeight="1">
-      <c t="s" r="A52" s="6">
-        <v>13</v>
-      </c>
-      <c r="B52" s="7">
-        <v>883</v>
-      </c>
-      <c t="s" r="C52" s="7">
-        <v>14</v>
-      </c>
+      <c r="A52" s="6"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c t="s" r="E52" s="7">
-        <v>105</v>
-      </c>
-      <c r="F52" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G52" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H52" s="8">
-        <v>112</v>
-      </c>
-      <c t="s" r="I52" s="7">
-        <v>113</v>
-      </c>
-      <c t="s" r="J52" s="7">
-        <v>114</v>
-      </c>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="7"/>
+      <c r="J52" s="7"/>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c r="M52" s="7"/>
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c t="s" r="A53" s="6">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B53" s="7">
-        <v>884</v>
+        <v>401</v>
       </c>
       <c t="s" r="C53" s="7">
         <v>14</v>
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c t="s" r="H53" s="8">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c r="M53" s="7"/>
     </row>
     <row r="54" ht="14.25" customHeight="1">
-      <c r="A54" s="6"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
+      <c t="s" r="A54" s="6">
+        <v>13</v>
+      </c>
+      <c r="B54" s="7">
+        <v>798</v>
+      </c>
+      <c t="s" r="C54" s="7">
+        <v>14</v>
+      </c>
       <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
+      <c t="s" r="E54" s="7">
+        <v>115</v>
+      </c>
+      <c r="F54" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G54" s="8">
+        <v>116</v>
+      </c>
+      <c t="s" r="H54" s="8">
+        <v>103</v>
+      </c>
+      <c t="s" r="I54" s="7">
+        <v>119</v>
+      </c>
+      <c t="s" r="J54" s="7">
+        <v>120</v>
+      </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c r="M54" s="7"/>
@@ -3171,29 +3208,29 @@
         <v>13</v>
       </c>
       <c r="B55" s="7">
-        <v>401</v>
+        <v>799</v>
       </c>
       <c t="s" r="C55" s="7">
         <v>14</v>
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>47</v>
+        <v>103</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3204,26 +3241,26 @@
         <v>13</v>
       </c>
       <c r="B56" s="7">
-        <v>798</v>
+        <v>402</v>
       </c>
       <c t="s" r="C56" s="7">
         <v>14</v>
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c t="s" r="J56" s="7">
         <v>122</v>
@@ -3237,29 +3274,29 @@
         <v>13</v>
       </c>
       <c r="B57" s="7">
-        <v>799</v>
+        <v>567</v>
       </c>
       <c t="s" r="C57" s="7">
         <v>14</v>
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3270,63 +3307,45 @@
         <v>13</v>
       </c>
       <c r="B58" s="7">
-        <v>402</v>
+        <v>568</v>
       </c>
       <c t="s" r="C58" s="7">
         <v>14</v>
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c r="M58" s="7"/>
     </row>
     <row r="59" ht="14.25" customHeight="1">
-      <c t="s" r="A59" s="6">
-        <v>13</v>
-      </c>
-      <c r="B59" s="7">
-        <v>567</v>
-      </c>
-      <c t="s" r="C59" s="7">
-        <v>14</v>
-      </c>
+      <c r="A59" s="6"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
       <c r="D59" s="7"/>
-      <c t="s" r="E59" s="7">
-        <v>117</v>
-      </c>
-      <c r="F59" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G59" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="H59" s="8">
-        <v>125</v>
-      </c>
-      <c t="s" r="I59" s="7">
-        <v>53</v>
-      </c>
-      <c t="s" r="J59" s="7">
-        <v>126</v>
-      </c>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="7"/>
+      <c r="J59" s="7"/>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c r="M59" s="7"/>
@@ -3336,95 +3355,123 @@
         <v>13</v>
       </c>
       <c r="B60" s="7">
-        <v>568</v>
+        <v>969</v>
       </c>
       <c t="s" r="C60" s="7">
         <v>14</v>
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
+      <c t="s" r="M60" s="7">
+        <v>121</v>
+      </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
-      <c r="A61" s="6"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
+      <c t="s" r="A61" s="6">
+        <v>13</v>
+      </c>
+      <c r="B61" s="7">
+        <v>986</v>
+      </c>
+      <c t="s" r="C61" s="7">
+        <v>14</v>
+      </c>
       <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
+      <c t="s" r="E61" s="7">
+        <v>126</v>
+      </c>
+      <c r="F61" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G61" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H61" s="8">
+        <v>130</v>
+      </c>
+      <c t="s" r="I61" s="7">
+        <v>131</v>
+      </c>
+      <c t="s" r="J61" s="7">
+        <v>132</v>
+      </c>
+      <c t="s" r="K61" s="7">
+        <v>106</v>
+      </c>
       <c r="L61" s="7"/>
-      <c r="M61" s="7"/>
+      <c t="s" r="M61" s="7">
+        <v>133</v>
+      </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c t="s" r="A62" s="6">
         <v>13</v>
       </c>
       <c r="B62" s="7">
-        <v>969</v>
+        <v>985</v>
       </c>
       <c t="s" r="C62" s="7">
         <v>14</v>
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>131</v>
-      </c>
-      <c r="K62" s="7"/>
+        <v>54</v>
+      </c>
+      <c t="s" r="K62" s="7">
+        <v>76</v>
+      </c>
       <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
+      <c t="s" r="M62" s="7">
+        <v>134</v>
+      </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c t="s" r="A63" s="6">
         <v>13</v>
       </c>
       <c r="B63" s="7">
-        <v>986</v>
+        <v>322</v>
       </c>
       <c t="s" r="C63" s="7">
         <v>14</v>
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3433,47 +3480,29 @@
         <v>20</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
     </row>
     <row r="64" ht="14.25" customHeight="1">
-      <c t="s" r="A64" s="6">
-        <v>13</v>
-      </c>
-      <c r="B64" s="7">
-        <v>985</v>
-      </c>
-      <c t="s" r="C64" s="7">
-        <v>14</v>
-      </c>
+      <c r="A64" s="6"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
       <c r="D64" s="7"/>
-      <c t="s" r="E64" s="7">
-        <v>128</v>
-      </c>
-      <c r="F64" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G64" s="8">
-        <v>132</v>
-      </c>
-      <c t="s" r="H64" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I64" s="7">
-        <v>36</v>
-      </c>
-      <c t="s" r="J64" s="7">
-        <v>54</v>
-      </c>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c r="M64" s="7"/>
@@ -3483,45 +3512,65 @@
         <v>13</v>
       </c>
       <c r="B65" s="7">
-        <v>322</v>
+        <v>1242</v>
       </c>
       <c t="s" r="C65" s="7">
         <v>14</v>
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>16</v>
+        <v>138</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
+      <c t="s" r="M65" s="7">
+        <v>140</v>
+      </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
-      <c r="A66" s="6"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
+      <c t="s" r="A66" s="6">
+        <v>13</v>
+      </c>
+      <c r="B66" s="7">
+        <v>1241</v>
+      </c>
+      <c t="s" r="C66" s="7">
+        <v>14</v>
+      </c>
       <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="7"/>
-      <c r="J66" s="7"/>
+      <c t="s" r="E66" s="7">
+        <v>137</v>
+      </c>
+      <c r="F66" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G66" s="8">
+        <v>138</v>
+      </c>
+      <c t="s" r="H66" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I66" s="7">
+        <v>119</v>
+      </c>
+      <c t="s" r="J66" s="7">
+        <v>141</v>
+      </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
@@ -3531,7 +3580,7 @@
         <v>13</v>
       </c>
       <c r="B67" s="7">
-        <v>1242</v>
+        <v>252</v>
       </c>
       <c t="s" r="C67" s="7">
         <v>14</v>
@@ -3550,10 +3599,10 @@
         <v>138</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3564,7 +3613,7 @@
         <v>13</v>
       </c>
       <c r="B68" s="7">
-        <v>1241</v>
+        <v>253</v>
       </c>
       <c t="s" r="C68" s="7">
         <v>14</v>
@@ -3583,10 +3632,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3597,7 +3646,7 @@
         <v>13</v>
       </c>
       <c r="B69" s="7">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c t="s" r="C69" s="7">
         <v>14</v>
@@ -3613,13 +3662,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H69" s="8">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3630,7 +3679,7 @@
         <v>13</v>
       </c>
       <c r="B70" s="7">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c t="s" r="C70" s="7">
         <v>14</v>
@@ -3643,50 +3692,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c t="s" r="H70" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c r="M70" s="7"/>
     </row>
     <row r="71" ht="14.25" customHeight="1">
-      <c t="s" r="A71" s="6">
-        <v>13</v>
-      </c>
-      <c r="B71" s="7">
-        <v>216</v>
-      </c>
-      <c t="s" r="C71" s="7">
-        <v>14</v>
-      </c>
+      <c r="A71" s="6"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
       <c r="D71" s="7"/>
-      <c t="s" r="E71" s="7">
-        <v>137</v>
-      </c>
-      <c r="F71" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G71" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H71" s="8">
-        <v>101</v>
-      </c>
-      <c t="s" r="I71" s="7">
-        <v>144</v>
-      </c>
-      <c t="s" r="J71" s="7">
-        <v>145</v>
-      </c>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="7"/>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c r="M71" s="7"/>
@@ -3696,45 +3727,65 @@
         <v>13</v>
       </c>
       <c r="B72" s="7">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c t="s" r="C72" s="7">
         <v>14</v>
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
-      <c r="M72" s="7"/>
+      <c t="s" r="M72" s="7">
+        <v>149</v>
+      </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
-      <c r="A73" s="6"/>
-      <c r="B73" s="7"/>
-      <c r="C73" s="7"/>
+      <c t="s" r="A73" s="6">
+        <v>13</v>
+      </c>
+      <c r="B73" s="7">
+        <v>741</v>
+      </c>
+      <c t="s" r="C73" s="7">
+        <v>14</v>
+      </c>
       <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="7"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="7"/>
+      <c t="s" r="E73" s="7">
+        <v>147</v>
+      </c>
+      <c r="F73" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G73" s="8">
+        <v>103</v>
+      </c>
+      <c t="s" r="H73" s="8">
+        <v>150</v>
+      </c>
+      <c t="s" r="I73" s="7">
+        <v>151</v>
+      </c>
+      <c t="s" r="J73" s="7">
+        <v>91</v>
+      </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c r="M73" s="7"/>
@@ -3744,64 +3795,62 @@
         <v>13</v>
       </c>
       <c r="B74" s="7">
-        <v>224</v>
+        <v>740</v>
       </c>
       <c t="s" r="C74" s="7">
         <v>14</v>
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
-      <c t="s" r="M74" s="7">
-        <v>150</v>
-      </c>
+      <c r="M74" s="7"/>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c t="s" r="A75" s="6">
         <v>13</v>
       </c>
       <c r="B75" s="7">
-        <v>741</v>
+        <v>227</v>
       </c>
       <c t="s" r="C75" s="7">
         <v>14</v>
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="H75" s="8">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3812,29 +3861,29 @@
         <v>13</v>
       </c>
       <c r="B76" s="7">
-        <v>740</v>
+        <v>278</v>
       </c>
       <c t="s" r="C76" s="7">
         <v>14</v>
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3845,29 +3894,29 @@
         <v>13</v>
       </c>
       <c r="B77" s="7">
-        <v>227</v>
+        <v>279</v>
       </c>
       <c t="s" r="C77" s="7">
         <v>14</v>
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3878,14 +3927,14 @@
         <v>13</v>
       </c>
       <c r="B78" s="7">
-        <v>278</v>
+        <v>154</v>
       </c>
       <c t="s" r="C78" s="7">
         <v>14</v>
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3894,47 +3943,33 @@
         <v>16</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>53</v>
-      </c>
-      <c r="K78" s="7"/>
+        <v>157</v>
+      </c>
+      <c t="s" r="K78" s="7">
+        <v>158</v>
+      </c>
       <c r="L78" s="7"/>
-      <c r="M78" s="7"/>
+      <c t="s" r="M78" s="7">
+        <v>159</v>
+      </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
-      <c t="s" r="A79" s="6">
-        <v>13</v>
-      </c>
-      <c r="B79" s="7">
-        <v>279</v>
-      </c>
-      <c t="s" r="C79" s="7">
-        <v>14</v>
-      </c>
+      <c r="A79" s="6"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
       <c r="D79" s="7"/>
-      <c t="s" r="E79" s="7">
-        <v>148</v>
-      </c>
-      <c r="F79" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G79" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="H79" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I79" s="7">
-        <v>156</v>
-      </c>
-      <c t="s" r="J79" s="7">
-        <v>54</v>
-      </c>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c r="M79" s="7"/>
@@ -3944,49 +3979,65 @@
         <v>13</v>
       </c>
       <c r="B80" s="7">
-        <v>154</v>
+        <v>501</v>
       </c>
       <c t="s" r="C80" s="7">
         <v>14</v>
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>158</v>
-      </c>
-      <c t="s" r="K80" s="7">
-        <v>159</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="81" ht="14.25" customHeight="1">
+      <c t="s" r="A81" s="6">
+        <v>13</v>
+      </c>
+      <c r="B81" s="7">
+        <v>514</v>
+      </c>
+      <c t="s" r="C81" s="7">
+        <v>14</v>
+      </c>
+      <c r="D81" s="7"/>
+      <c t="s" r="E81" s="7">
         <v>160</v>
       </c>
-    </row>
-    <row r="81" ht="14.25" customHeight="1">
-      <c r="A81" s="6"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="7"/>
+      <c r="F81" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G81" s="8">
+        <v>161</v>
+      </c>
+      <c t="s" r="H81" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="I81" s="7">
+        <v>164</v>
+      </c>
+      <c t="s" r="J81" s="7">
+        <v>118</v>
+      </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c r="M81" s="7"/>
@@ -3996,14 +4047,14 @@
         <v>13</v>
       </c>
       <c r="B82" s="7">
-        <v>501</v>
+        <v>563</v>
       </c>
       <c t="s" r="C82" s="7">
         <v>14</v>
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4012,13 +4063,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4029,29 +4080,29 @@
         <v>13</v>
       </c>
       <c r="B83" s="7">
-        <v>514</v>
+        <v>564</v>
       </c>
       <c t="s" r="C83" s="7">
         <v>14</v>
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4062,14 +4113,14 @@
         <v>13</v>
       </c>
       <c r="B84" s="7">
-        <v>563</v>
+        <v>787</v>
       </c>
       <c t="s" r="C84" s="7">
         <v>14</v>
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4078,13 +4129,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4095,29 +4146,29 @@
         <v>13</v>
       </c>
       <c r="B85" s="7">
-        <v>564</v>
+        <v>774</v>
       </c>
       <c t="s" r="C85" s="7">
         <v>14</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4128,14 +4179,14 @@
         <v>13</v>
       </c>
       <c r="B86" s="7">
-        <v>787</v>
+        <v>517</v>
       </c>
       <c t="s" r="C86" s="7">
         <v>14</v>
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4144,13 +4195,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>51</v>
+        <v>170</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4161,63 +4212,45 @@
         <v>13</v>
       </c>
       <c r="B87" s="7">
-        <v>774</v>
+        <v>520</v>
       </c>
       <c t="s" r="C87" s="7">
         <v>14</v>
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
+        <v>160</v>
+      </c>
+      <c r="F87" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G87" s="8">
         <v>161</v>
-      </c>
-      <c r="F87" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G87" s="8">
-        <v>165</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
     </row>
     <row r="88" ht="14.25" customHeight="1">
-      <c t="s" r="A88" s="6">
-        <v>13</v>
-      </c>
-      <c r="B88" s="7">
-        <v>517</v>
-      </c>
-      <c t="s" r="C88" s="7">
-        <v>14</v>
-      </c>
+      <c r="A88" s="6"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="7"/>
       <c r="D88" s="7"/>
-      <c t="s" r="E88" s="7">
-        <v>161</v>
-      </c>
-      <c r="F88" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G88" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="H88" s="8">
-        <v>162</v>
-      </c>
-      <c t="s" r="I88" s="7">
-        <v>167</v>
-      </c>
-      <c t="s" r="J88" s="7">
-        <v>168</v>
-      </c>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="7"/>
+      <c r="J88" s="7"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
@@ -4227,45 +4260,63 @@
         <v>13</v>
       </c>
       <c r="B89" s="7">
-        <v>520</v>
+        <v>921</v>
       </c>
       <c t="s" r="C89" s="7">
         <v>14</v>
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
     </row>
     <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="6"/>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
+      <c t="s" r="A90" s="6">
+        <v>13</v>
+      </c>
+      <c r="B90" s="7">
+        <v>525</v>
+      </c>
+      <c t="s" r="C90" s="7">
+        <v>14</v>
+      </c>
       <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="7"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="7"/>
-      <c r="J90" s="7"/>
+      <c t="s" r="E90" s="7">
+        <v>172</v>
+      </c>
+      <c r="F90" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G90" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H90" s="8">
+        <v>161</v>
+      </c>
+      <c t="s" r="I90" s="7">
+        <v>80</v>
+      </c>
+      <c t="s" r="J90" s="7">
+        <v>176</v>
+      </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c r="M90" s="7"/>
@@ -4275,29 +4326,29 @@
         <v>13</v>
       </c>
       <c r="B91" s="7">
-        <v>921</v>
+        <v>528</v>
       </c>
       <c t="s" r="C91" s="7">
         <v>14</v>
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>173</v>
+        <v>52</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4308,14 +4359,14 @@
         <v>13</v>
       </c>
       <c r="B92" s="7">
-        <v>525</v>
+        <v>971</v>
       </c>
       <c t="s" r="C92" s="7">
         <v>14</v>
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4324,13 +4375,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4338,114 +4389,114 @@
     </row>
     <row r="93" ht="14.25" customHeight="1">
       <c t="s" r="A93" s="6">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B93" s="7">
-        <v>528</v>
+        <v>972</v>
       </c>
       <c t="s" r="C93" s="7">
         <v>14</v>
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>52</v>
+        <v>162</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
     </row>
     <row r="94" ht="14.25" customHeight="1">
-      <c t="s" r="A94" s="6">
-        <v>13</v>
-      </c>
-      <c r="B94" s="7">
-        <v>971</v>
-      </c>
-      <c t="s" r="C94" s="7">
-        <v>14</v>
-      </c>
+      <c r="A94" s="6"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="7"/>
       <c r="D94" s="7"/>
-      <c t="s" r="E94" s="7">
-        <v>170</v>
-      </c>
-      <c r="F94" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G94" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="H94" s="8">
-        <v>176</v>
-      </c>
-      <c t="s" r="I94" s="7">
-        <v>113</v>
-      </c>
-      <c t="s" r="J94" s="7">
-        <v>177</v>
-      </c>
+      <c r="E94" s="7"/>
+      <c r="F94" s="7"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="7"/>
+      <c r="J94" s="7"/>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c t="s" r="A95" s="6">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B95" s="7">
-        <v>972</v>
+        <v>729</v>
       </c>
       <c t="s" r="C95" s="7">
         <v>14</v>
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
     </row>
     <row r="96" ht="14.25" customHeight="1">
-      <c r="A96" s="6"/>
-      <c r="B96" s="7"/>
-      <c r="C96" s="7"/>
+      <c t="s" r="A96" s="6">
+        <v>13</v>
+      </c>
+      <c r="B96" s="7">
+        <v>728</v>
+      </c>
+      <c t="s" r="C96" s="7">
+        <v>14</v>
+      </c>
       <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="7"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
-      <c r="I96" s="7"/>
-      <c r="J96" s="7"/>
+      <c t="s" r="E96" s="7">
+        <v>181</v>
+      </c>
+      <c r="F96" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G96" s="8">
+        <v>116</v>
+      </c>
+      <c t="s" r="H96" s="8">
+        <v>161</v>
+      </c>
+      <c t="s" r="I96" s="7">
+        <v>131</v>
+      </c>
+      <c t="s" r="J96" s="7">
+        <v>34</v>
+      </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c r="M96" s="7"/>
@@ -4455,29 +4506,29 @@
         <v>13</v>
       </c>
       <c r="B97" s="7">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c t="s" r="C97" s="7">
         <v>14</v>
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>181</v>
+        <v>53</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4488,29 +4539,29 @@
         <v>13</v>
       </c>
       <c r="B98" s="7">
-        <v>728</v>
+        <v>714</v>
       </c>
       <c t="s" r="C98" s="7">
         <v>14</v>
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4521,63 +4572,45 @@
         <v>13</v>
       </c>
       <c r="B99" s="7">
-        <v>715</v>
+        <v>631</v>
       </c>
       <c t="s" r="C99" s="7">
         <v>14</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c r="M99" s="7"/>
     </row>
     <row r="100" ht="15" customHeight="1">
-      <c t="s" r="A100" s="6">
-        <v>13</v>
-      </c>
-      <c r="B100" s="7">
-        <v>714</v>
-      </c>
-      <c t="s" r="C100" s="7">
-        <v>14</v>
-      </c>
+      <c r="A100" s="6"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="7"/>
       <c r="D100" s="7"/>
-      <c t="s" r="E100" s="7">
-        <v>179</v>
-      </c>
-      <c r="F100" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G100" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H100" s="8">
-        <v>162</v>
-      </c>
-      <c t="s" r="I100" s="7">
-        <v>183</v>
-      </c>
-      <c t="s" r="J100" s="7">
-        <v>77</v>
-      </c>
+      <c r="E100" s="7"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="7"/>
+      <c r="J100" s="7"/>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
@@ -4587,48 +4620,74 @@
         <v>13</v>
       </c>
       <c r="B101" s="7">
-        <v>631</v>
+        <v>126</v>
       </c>
       <c t="s" r="C101" s="7">
         <v>14</v>
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G101" s="8">
-        <v>162</v>
+        <v>16</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>185</v>
-      </c>
-      <c r="K101" s="7"/>
+        <v>30</v>
+      </c>
+      <c t="s" r="K101" s="7">
+        <v>189</v>
+      </c>
       <c r="L101" s="7"/>
-      <c r="M101" s="7"/>
+      <c t="s" r="M101" s="7">
+        <v>190</v>
+      </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c r="A102" s="6"/>
-      <c r="B102" s="7"/>
-      <c r="C102" s="7"/>
+      <c t="s" r="A102" s="6">
+        <v>13</v>
+      </c>
+      <c r="B102" s="7">
+        <v>131</v>
+      </c>
+      <c t="s" r="C102" s="7">
+        <v>14</v>
+      </c>
       <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="8"/>
-      <c r="H102" s="8"/>
-      <c r="I102" s="7"/>
-      <c r="J102" s="7"/>
-      <c r="K102" s="7"/>
+      <c t="s" r="E102" s="7">
+        <v>188</v>
+      </c>
+      <c r="F102" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G102" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H102" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I102" s="7">
+        <v>191</v>
+      </c>
+      <c t="s" r="J102" s="7">
+        <v>166</v>
+      </c>
+      <c t="s" r="K102" s="7">
+        <v>192</v>
+      </c>
       <c r="L102" s="7"/>
-      <c r="M102" s="7"/>
+      <c t="s" r="M102" s="7">
+        <v>193</v>
+      </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
       <c t="s" r="A103" s="6">
@@ -4642,7 +4701,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4654,14 +4713,18 @@
         <v>28</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>135</v>
       </c>
-      <c r="K103" s="7"/>
+      <c t="s" r="K103" s="7">
+        <v>142</v>
+      </c>
       <c r="L103" s="7"/>
-      <c r="M103" s="7"/>
+      <c t="s" r="M103" s="7">
+        <v>194</v>
+      </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
       <c t="s" r="A104" s="6">
@@ -4675,7 +4738,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4687,14 +4750,18 @@
         <v>16</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>56</v>
       </c>
-      <c r="K104" s="7"/>
+      <c t="s" r="K104" s="7">
+        <v>196</v>
+      </c>
       <c r="L104" s="7"/>
-      <c r="M104" s="7"/>
+      <c t="s" r="M104" s="7">
+        <v>197</v>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="6"/>
@@ -4723,7 +4790,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4735,10 +4802,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4756,7 +4823,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4765,10 +4832,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>19</v>
@@ -4789,22 +4856,22 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4822,7 +4889,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4831,7 +4898,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I109" s="7">
         <v>93</v>
@@ -4855,13 +4922,13 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>16</v>
@@ -4870,7 +4937,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4888,7 +4955,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4897,13 +4964,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I111" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4921,13 +4988,13 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>16</v>
@@ -4936,7 +5003,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4969,7 +5036,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -4981,15 +5048,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5004,7 +5071,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5019,7 +5086,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5037,7 +5104,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5049,10 +5116,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5070,7 +5137,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5079,13 +5146,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5103,19 +5170,19 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>143</v>
@@ -5136,7 +5203,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5148,10 +5215,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5169,7 +5236,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5181,10 +5248,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5217,7 +5284,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5229,7 +5296,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>51</v>
@@ -5250,7 +5317,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5262,7 +5329,7 @@
         <v>138</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>38</v>
@@ -5272,7 +5339,7 @@
       </c>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>144</v>
+        <v>134</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5287,7 +5354,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5299,17 +5366,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c t="s" r="K124" s="7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5335,11 +5402,11 @@
         <v>2983</v>
       </c>
       <c t="s" r="C126" s="7">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5351,13 +5418,13 @@
         <v>20</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>91</v>
       </c>
       <c t="s" r="K126" s="7">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
@@ -5376,7 +5443,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5388,10 +5455,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5409,7 +5476,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5424,7 +5491,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5442,7 +5509,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5475,7 +5542,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5484,13 +5551,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5523,22 +5590,22 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5556,7 +5623,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5565,13 +5632,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5589,22 +5656,22 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5622,7 +5689,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5631,13 +5698,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I135" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5655,22 +5722,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5688,7 +5755,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5697,13 +5764,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5721,13 +5788,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>16</v>
@@ -5736,7 +5803,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5765,11 +5832,11 @@
         <v>7621</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5778,13 +5845,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I140" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5798,26 +5865,26 @@
         <v>7614</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5831,11 +5898,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5844,7 +5911,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c t="s" r="I142" s="7">
         <v>43</v>
@@ -5883,7 +5950,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5895,14 +5962,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
-      <c r="M144" s="7"/>
+      <c t="s" r="M144" s="7">
+        <v>236</v>
+      </c>
     </row>
     <row r="145" ht="15" customHeight="1">
       <c t="s" r="A145" s="6">
@@ -5916,7 +5985,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5928,10 +5997,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5949,7 +6018,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5961,10 +6030,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5982,7 +6051,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -5994,10 +6063,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6015,7 +6084,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6027,10 +6096,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6048,7 +6117,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6060,7 +6129,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>38</v>
@@ -6081,7 +6150,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6114,7 +6183,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6126,10 +6195,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6162,7 +6231,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6171,13 +6240,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6195,13 +6264,13 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>47</v>
@@ -6210,7 +6279,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6228,7 +6297,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6240,10 +6309,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6261,7 +6330,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6270,13 +6339,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6294,19 +6363,19 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>85</v>
@@ -6342,7 +6411,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6351,13 +6420,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6375,22 +6444,22 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6408,7 +6477,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6417,10 +6486,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>41</v>
@@ -6441,22 +6510,22 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6489,29 +6558,29 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="K164" s="7">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -6526,7 +6595,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6538,10 +6607,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6559,7 +6628,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6571,10 +6640,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6592,7 +6661,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6601,13 +6670,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6625,22 +6694,22 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6673,7 +6742,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6682,10 +6751,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c t="s" r="J170" s="7">
         <v>34</v>
@@ -6706,19 +6775,19 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>77</v>
@@ -6739,7 +6808,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6748,20 +6817,20 @@
         <v>47</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I172" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c t="s" r="K172" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -6776,19 +6845,19 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>97</v>
@@ -6824,7 +6893,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6833,17 +6902,19 @@
         <v>47</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
-      <c r="M175" s="7"/>
+      <c t="s" r="M175" s="7">
+        <v>267</v>
+      </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c t="s" r="A176" s="6">
@@ -6857,22 +6928,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>260</v>
+        <v>189</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6890,7 +6961,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6899,10 +6970,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c t="s" r="J177" s="7">
         <v>34</v>
@@ -6923,22 +6994,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6956,7 +7027,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6971,7 +7042,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6989,7 +7060,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7001,10 +7072,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7022,7 +7093,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7031,13 +7102,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7055,22 +7126,22 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7103,7 +7174,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7115,10 +7186,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7136,7 +7207,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7145,13 +7216,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7169,13 +7240,13 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>47</v>
@@ -7184,7 +7255,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7217,7 +7288,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7229,10 +7300,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7250,7 +7321,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7262,10 +7333,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>107</v>
+        <v>191</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7283,7 +7354,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7298,7 +7369,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7316,7 +7387,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7331,7 +7402,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7349,7 +7420,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7358,13 +7429,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7382,22 +7453,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7430,7 +7501,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7442,10 +7513,10 @@
         <v>90</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>273</v>
+        <v>193</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7463,7 +7534,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7475,10 +7546,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7496,7 +7567,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7505,13 +7576,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7529,22 +7600,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7577,7 +7648,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7586,17 +7657,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
-      <c r="M200" s="7"/>
+      <c t="s" r="M200" s="7">
+        <v>284</v>
+      </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c t="s" r="A201" s="6">
@@ -7610,13 +7683,13 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>16</v>
@@ -7643,7 +7716,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7655,10 +7728,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7676,7 +7749,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7691,7 +7764,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7709,7 +7782,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7721,10 +7794,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7742,7 +7815,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7751,13 +7824,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7775,22 +7848,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>281</v>
+        <v>194</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7808,7 +7881,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7820,10 +7893,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7856,7 +7929,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7865,13 +7938,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="I209" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7889,13 +7962,13 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>16</v>
@@ -7904,7 +7977,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7922,7 +7995,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7931,13 +8004,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -7955,19 +8028,19 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>24</v>
@@ -7988,7 +8061,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7997,13 +8070,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8036,7 +8109,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8045,13 +8118,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8069,19 +8142,19 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>36</v>
@@ -8102,7 +8175,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8117,14 +8190,14 @@
         <v>53</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c t="s" r="K217" s="7">
         <v>52</v>
       </c>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8154,7 +8227,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8163,17 +8236,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="I219" s="7">
         <v>99</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
-      <c r="M219" s="7"/>
+      <c t="s" r="M219" s="7">
+        <v>300</v>
+      </c>
     </row>
     <row r="220" ht="15" customHeight="1">
       <c t="s" r="A220" s="6">
@@ -8187,13 +8262,13 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>16</v>
@@ -8202,7 +8277,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8220,7 +8295,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8232,10 +8307,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8253,7 +8328,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8268,7 +8343,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8286,7 +8361,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8298,10 +8373,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="K223" s="7">
         <v>93</v>
@@ -8323,7 +8398,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8335,13 +8410,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c t="s" r="K224" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
@@ -8360,7 +8435,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8369,20 +8444,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8397,29 +8472,29 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="K226" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -8449,26 +8524,28 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
-      <c r="M228" s="7"/>
+      <c t="s" r="M228" s="7">
+        <v>225</v>
+      </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
       <c t="s" r="A229" s="6">
@@ -8482,7 +8559,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8491,13 +8568,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8515,29 +8592,29 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="K230" s="7">
         <v>21</v>
       </c>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -8552,7 +8629,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8585,7 +8662,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8597,7 +8674,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>96</v>
@@ -8633,7 +8710,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8645,7 +8722,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>92</v>
@@ -8666,7 +8743,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8675,7 +8752,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c t="s" r="I235" s="7">
         <v>93</v>
@@ -8699,19 +8776,19 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>26</v>
@@ -8732,7 +8809,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8747,7 +8824,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8780,7 +8857,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8792,10 +8869,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>273</v>
+        <v>193</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8813,7 +8890,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8822,13 +8899,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8846,19 +8923,19 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>143</v>
@@ -8879,7 +8956,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8888,13 +8965,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8927,7 +9004,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8936,10 +9013,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>48</v>
@@ -8947,7 +9024,7 @@
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>303</v>
+        <v>105</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -8962,29 +9039,29 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c t="s" r="K245" s="7">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9014,7 +9091,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9026,7 +9103,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>91</v>
@@ -9047,7 +9124,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9059,10 +9136,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9080,7 +9157,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9092,7 +9169,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>49</v>
@@ -9113,7 +9190,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9146,7 +9223,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9155,13 +9232,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9179,13 +9256,13 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>47</v>
@@ -9194,7 +9271,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9212,7 +9289,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9221,13 +9298,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9260,7 +9337,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9272,15 +9349,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9295,7 +9372,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9304,13 +9381,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9328,13 +9405,13 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>47</v>
@@ -9343,7 +9420,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9361,7 +9438,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9370,10 +9447,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>37</v>
@@ -9394,13 +9471,13 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>47</v>
@@ -9409,7 +9486,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9442,22 +9519,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9475,22 +9552,22 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="I262" s="7">
         <v>21</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9508,22 +9585,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9541,22 +9618,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9574,22 +9651,22 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9607,7 +9684,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9619,10 +9696,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9655,13 +9732,13 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>16</v>
@@ -9670,7 +9747,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9688,7 +9765,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9697,13 +9774,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c t="s" r="I269" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9721,22 +9798,22 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9754,7 +9831,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9769,7 +9846,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9802,7 +9879,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9811,17 +9888,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
-      <c r="M273" s="7"/>
+      <c t="s" r="M273" s="7">
+        <v>326</v>
+      </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
       <c t="s" r="A274" s="6">
@@ -9835,22 +9914,22 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9868,7 +9947,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9877,13 +9956,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9901,22 +9980,22 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9934,7 +10013,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -9943,13 +10022,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>34</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9967,13 +10046,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>47</v>
@@ -10004,7 +10083,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10016,10 +10095,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10052,7 +10131,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10061,17 +10140,19 @@
         <v>47</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>100</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
-      <c r="M281" s="7"/>
+      <c t="s" r="M281" s="7">
+        <v>60</v>
+      </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
       <c t="s" r="A282" s="6">
@@ -10085,22 +10166,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10118,7 +10199,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10127,13 +10208,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10151,22 +10232,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10184,7 +10265,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10193,13 +10274,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10217,19 +10298,19 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>135</v>
@@ -10265,22 +10346,22 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10298,7 +10379,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10310,7 +10391,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>36</v>
@@ -10331,7 +10412,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10343,10 +10424,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10364,7 +10445,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10373,13 +10454,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I291" s="7">
         <v>135</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>281</v>
+        <v>194</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10412,19 +10493,19 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>92</v>
@@ -10445,22 +10526,22 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10478,19 +10559,19 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>87</v>
@@ -10511,22 +10592,22 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10559,7 +10640,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10571,10 +10652,10 @@
         <v>138</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10592,7 +10673,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10607,7 +10688,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10625,7 +10706,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10634,13 +10715,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10658,19 +10739,19 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>87</v>
@@ -10706,13 +10787,13 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>16</v>
@@ -10721,11 +10802,13 @@
         <v>97</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
-      <c r="M303" s="7"/>
+      <c t="s" r="M303" s="7">
+        <v>341</v>
+      </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
       <c t="s" r="A304" s="6">
@@ -10739,7 +10822,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10748,13 +10831,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10772,22 +10855,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="I305" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10805,22 +10888,22 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10838,22 +10921,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10871,22 +10954,22 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10904,22 +10987,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -10952,7 +11035,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -10961,17 +11044,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
-      <c r="M311" s="7"/>
+      <c t="s" r="M311" s="7">
+        <v>346</v>
+      </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
       <c t="s" r="A312" s="6">
@@ -10985,22 +11070,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11018,7 +11103,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11027,10 +11112,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>34</v>
@@ -11051,22 +11136,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11084,7 +11169,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11093,13 +11178,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11117,19 +11202,19 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>88</v>
@@ -11165,7 +11250,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11174,13 +11259,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11194,26 +11279,26 @@
         <v>8520</v>
       </c>
       <c t="s" r="C319" s="7">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11227,26 +11312,26 @@
         <v>8521</v>
       </c>
       <c t="s" r="C320" s="7">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11264,16 +11349,16 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>56</v>
@@ -11312,7 +11397,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11321,13 +11406,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11345,13 +11430,13 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>47</v>
@@ -11360,7 +11445,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11378,7 +11463,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11387,13 +11472,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11411,13 +11496,13 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>47</v>
@@ -11444,7 +11529,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11456,7 +11541,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>43</v>
@@ -11477,7 +11562,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11489,10 +11574,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11525,7 +11610,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11537,17 +11622,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c t="s" r="K330" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -11562,7 +11647,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11574,17 +11659,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>36</v>
       </c>
       <c t="s" r="K331" s="7">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -11599,7 +11684,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11608,13 +11693,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="I332" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11632,13 +11717,13 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>16</v>
@@ -11647,7 +11732,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>281</v>
+        <v>194</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11665,7 +11750,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11677,10 +11762,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11698,7 +11783,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11710,7 +11795,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>60</v>
@@ -11746,7 +11831,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11758,10 +11843,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11779,7 +11864,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11788,10 +11873,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>273</v>
+        <v>193</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>75</v>
@@ -11812,22 +11897,22 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11845,7 +11930,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11854,7 +11939,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>54</v>
@@ -11878,13 +11963,13 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>16</v>
@@ -11893,7 +11978,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11926,7 +12011,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11935,17 +12020,19 @@
         <v>47</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
-      <c r="M343" s="7"/>
+      <c t="s" r="M343" s="7">
+        <v>363</v>
+      </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
       <c t="s" r="A344" s="6">
@@ -11959,22 +12046,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11992,7 +12079,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12001,13 +12088,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12025,22 +12112,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12073,22 +12160,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12106,22 +12193,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12139,22 +12226,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12172,22 +12259,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12205,22 +12292,22 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12253,26 +12340,28 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
-      <c r="M354" s="7"/>
+      <c t="s" r="M354" s="7">
+        <v>372</v>
+      </c>
     </row>
     <row r="355" ht="15" customHeight="1">
       <c t="s" r="A355" s="6">
@@ -12286,7 +12375,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12295,13 +12384,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12319,13 +12408,13 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>47</v>
@@ -12334,7 +12423,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12352,7 +12441,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12361,10 +12450,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>37</v>
@@ -12385,13 +12474,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>47</v>
@@ -12400,7 +12489,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12418,7 +12507,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12427,13 +12516,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12466,19 +12555,19 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>18</v>
@@ -12499,7 +12588,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12508,13 +12597,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I362" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12532,19 +12621,19 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>81</v>
@@ -12565,7 +12654,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12574,13 +12663,13 @@
         <v>72</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12594,26 +12683,26 @@
         <v>8020</v>
       </c>
       <c t="s" r="C365" s="7">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12627,26 +12716,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C366" s="7">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12679,7 +12768,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12691,10 +12780,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12712,7 +12801,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12721,13 +12810,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12745,22 +12834,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12778,7 +12867,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12790,10 +12879,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12811,7 +12900,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12820,13 +12909,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12844,22 +12933,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12892,7 +12981,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12901,13 +12990,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>73</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12925,19 +13014,19 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>34</v>
@@ -12958,7 +13047,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -12967,13 +13056,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c t="s" r="I377" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12991,19 +13080,19 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J378" s="7">
         <v>76</v>
@@ -13024,7 +13113,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13033,13 +13122,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13057,22 +13146,22 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13105,7 +13194,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13138,7 +13227,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13150,10 +13239,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13171,7 +13260,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13183,10 +13272,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13215,11 +13304,11 @@
         <v>664</v>
       </c>
       <c t="s" r="C386" s="7">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F386" s="7">
         <v>330</v>
@@ -13228,13 +13317,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13252,22 +13341,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F387" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13285,29 +13374,29 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F388" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>107</v>
+        <v>191</v>
       </c>
       <c t="s" r="K388" s="7">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -13337,7 +13426,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F390" s="7">
         <v>330</v>
@@ -13346,13 +13435,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13370,22 +13459,22 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="F391" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13418,7 +13507,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
@@ -13427,10 +13516,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>96</v>
@@ -13451,22 +13540,22 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F394" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13499,7 +13588,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
@@ -13508,10 +13597,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>19</v>
@@ -13532,16 +13621,16 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c t="s" r="I397" s="7">
         <v>21</v>
@@ -13565,22 +13654,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>281</v>
+        <v>194</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13613,16 +13702,16 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>57</v>
@@ -13646,22 +13735,22 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13694,22 +13783,22 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13727,7 +13816,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -13736,13 +13825,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13750,7 +13839,7 @@
     </row>
     <row r="405" ht="16.5" customHeight="1">
       <c t="s" r="A405" s="9">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B405" s="9"/>
       <c r="C405" s="9"/>
@@ -13770,7 +13859,7 @@
     <row r="406" ht="65.25" customHeight="1"/>
     <row r="407" ht="16.5" customHeight="1">
       <c t="s" r="A407" s="10">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="B407" s="10"/>
       <c r="C407" s="10"/>
@@ -13783,7 +13872,7 @@
       <c r="J407" s="10"/>
       <c r="K407" s="10"/>
       <c t="s" r="L407" s="11">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="M407" s="11"/>
       <c r="N407" s="11"/>

--- a/Data/FlightPlan/FPL_22OCT26.xlsx
+++ b/Data/FlightPlan/FPL_22OCT26.xlsx
@@ -368,6 +368,9 @@
     <t>08:50</t>
   </si>
   <si>
+    <t>09:12</t>
+  </si>
+  <si>
     <t>09:20</t>
   </si>
   <si>
@@ -467,6 +470,9 @@
     <t>07:20</t>
   </si>
   <si>
+    <t>08:52</t>
+  </si>
+  <si>
     <t>09:15</t>
   </si>
   <si>
@@ -506,6 +512,9 @@
     <t>07:30</t>
   </si>
   <si>
+    <t>09:07</t>
+  </si>
+  <si>
     <t>11:05</t>
   </si>
   <si>
@@ -686,6 +695,9 @@
     <t>VN-A554</t>
   </si>
   <si>
+    <t>08:03</t>
+  </si>
+  <si>
     <t>10:30</t>
   </si>
   <si>
@@ -758,6 +770,9 @@
     <t>KHH</t>
   </si>
   <si>
+    <t>11:54</t>
+  </si>
+  <si>
     <t>14:50</t>
   </si>
   <si>
@@ -773,7 +788,7 @@
     <t>VN-A629</t>
   </si>
   <si>
-    <t>12:49</t>
+    <t>12:51</t>
   </si>
   <si>
     <t>21:25</t>
@@ -797,177 +812,183 @@
     <t>VN-A630</t>
   </si>
   <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:46</t>
+  </si>
+  <si>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>07:24</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
     <t>CGK</t>
   </si>
   <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>07:36</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>14:44</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>09:03</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
     <t>08:40</t>
   </si>
   <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:46</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>07:24</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>07:36</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>09:23</t>
-  </si>
-  <si>
     <t>VN-A651</t>
   </si>
   <si>
@@ -992,6 +1013,9 @@
     <t>06:53</t>
   </si>
   <si>
+    <t>08:24</t>
+  </si>
+  <si>
     <t>VN-A657</t>
   </si>
   <si>
@@ -1037,6 +1061,9 @@
     <t>06:49</t>
   </si>
   <si>
+    <t>08:57</t>
+  </si>
+  <si>
     <t>13:20</t>
   </si>
   <si>
@@ -1127,9 +1154,6 @@
     <t>VN-A683</t>
   </si>
   <si>
-    <t>12:27</t>
-  </si>
-  <si>
     <t>01:05</t>
   </si>
   <si>
@@ -1166,6 +1190,9 @@
     <t>VN-A697</t>
   </si>
   <si>
+    <t>14:07</t>
+  </si>
+  <si>
     <t>P</t>
   </si>
   <si>
@@ -1211,10 +1238,13 @@
     <t>SYD</t>
   </si>
   <si>
+    <t>16:44</t>
+  </si>
+  <si>
     <t>Total Record(s): 331</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 22, 2026 07:11</t>
+    <t xml:space="preserve">Generated on  Oct 22, 2026 07:57</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3168,7 +3198,9 @@
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
+      <c t="s" r="M53" s="7">
+        <v>119</v>
+      </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c t="s" r="A54" s="6">
@@ -3194,10 +3226,10 @@
         <v>103</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3227,7 +3259,7 @@
         <v>116</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J55" s="7">
         <v>21</v>
@@ -3263,7 +3295,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3290,13 +3322,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I57" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3320,13 +3352,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J58" s="7">
         <v>83</v>
@@ -3362,27 +3394,27 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3397,7 +3429,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3406,20 +3438,20 @@
         <v>20</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="K61" s="7">
         <v>106</v>
       </c>
       <c r="L61" s="7"/>
       <c t="s" r="M61" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -3434,13 +3466,13 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>20</v>
@@ -3456,7 +3488,7 @@
       </c>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -3471,7 +3503,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3483,10 +3515,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3519,7 +3551,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3528,10 +3560,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>118</v>
@@ -3539,7 +3571,7 @@
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -3554,22 +3586,22 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G66" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="H66" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3587,7 +3619,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3596,13 +3628,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3620,22 +3652,22 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3653,7 +3685,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3665,10 +3697,10 @@
         <v>103</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3686,7 +3718,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3698,10 +3730,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3734,7 +3766,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3746,15 +3778,15 @@
         <v>103</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -3769,7 +3801,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3778,17 +3810,19 @@
         <v>103</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J73" s="7">
         <v>91</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
-      <c r="M73" s="7"/>
+      <c t="s" r="M73" s="7">
+        <v>153</v>
+      </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
       <c t="s" r="A74" s="6">
@@ -3802,22 +3836,22 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>103</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3835,7 +3869,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3847,7 +3881,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>34</v>
@@ -3868,7 +3902,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3877,7 +3911,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H76" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I76" s="7">
         <v>49</v>
@@ -3901,19 +3935,19 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J77" s="7">
         <v>54</v>
@@ -3934,7 +3968,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3946,17 +3980,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c t="s" r="K78" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -3986,7 +4020,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -3995,10 +4029,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>117</v>
@@ -4006,7 +4040,7 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4021,26 +4055,28 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>118</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
-      <c r="M81" s="7"/>
+      <c t="s" r="M81" s="7">
+        <v>167</v>
+      </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c t="s" r="A82" s="6">
@@ -4054,7 +4090,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4063,10 +4099,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J82" s="7">
         <v>50</v>
@@ -4087,22 +4123,22 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H83" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4120,7 +4156,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4129,10 +4165,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c t="s" r="J84" s="7">
         <v>51</v>
@@ -4153,19 +4189,19 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>109</v>
@@ -4186,7 +4222,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4195,13 +4231,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4219,22 +4255,22 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4267,22 +4303,22 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4300,7 +4336,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4309,13 +4345,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I90" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4333,19 +4369,19 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>52</v>
@@ -4366,7 +4402,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4375,13 +4411,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="I92" s="7">
         <v>111</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4399,22 +4435,22 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4447,22 +4483,22 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H95" s="8">
         <v>116</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4480,7 +4516,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4489,10 +4525,10 @@
         <v>116</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>34</v>
@@ -4513,19 +4549,19 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>20</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>53</v>
@@ -4546,7 +4582,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4555,10 +4591,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>77</v>
@@ -4579,22 +4615,22 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4627,7 +4663,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4639,17 +4675,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>30</v>
       </c>
       <c t="s" r="K101" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -4664,7 +4700,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4676,17 +4712,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="K102" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -4701,7 +4737,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4713,17 +4749,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="K103" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -4738,7 +4774,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4750,17 +4786,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>56</v>
       </c>
       <c t="s" r="K104" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -4790,7 +4826,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4805,7 +4841,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4823,7 +4859,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4832,10 +4868,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>19</v>
@@ -4856,22 +4892,22 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4889,7 +4925,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4898,7 +4934,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I109" s="7">
         <v>93</v>
@@ -4922,13 +4958,13 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G110" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H110" s="8">
         <v>16</v>
@@ -4937,7 +4973,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4955,7 +4991,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4964,13 +5000,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I111" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4988,13 +5024,13 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>16</v>
@@ -5003,7 +5039,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5036,7 +5072,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5048,15 +5084,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5071,7 +5107,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5086,7 +5122,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5104,7 +5140,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5116,10 +5152,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5137,7 +5173,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5149,10 +5185,10 @@
         <v>116</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5170,7 +5206,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5182,10 +5218,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5203,7 +5239,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5215,10 +5251,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5236,7 +5272,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5248,10 +5284,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5284,7 +5320,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5296,7 +5332,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>51</v>
@@ -5317,7 +5353,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5326,10 +5362,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>38</v>
@@ -5339,7 +5375,7 @@
       </c>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5354,29 +5390,29 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="K124" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5402,11 +5438,11 @@
         <v>2983</v>
       </c>
       <c t="s" r="C126" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5418,13 +5454,13 @@
         <v>20</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>91</v>
       </c>
       <c t="s" r="K126" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
@@ -5443,7 +5479,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5455,10 +5491,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5476,7 +5512,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5509,7 +5545,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5542,7 +5578,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5551,13 +5587,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5590,26 +5626,28 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>104</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
-      <c r="M132" s="7"/>
+      <c t="s" r="M132" s="7">
+        <v>228</v>
+      </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
       <c t="s" r="A133" s="6">
@@ -5623,7 +5661,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5632,13 +5670,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H133" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5656,13 +5694,13 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G134" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H134" s="8">
         <v>16</v>
@@ -5671,7 +5709,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5689,7 +5727,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5698,13 +5736,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I135" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5722,22 +5760,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5755,7 +5793,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5764,13 +5802,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5788,13 +5826,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>16</v>
@@ -5803,7 +5841,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5832,11 +5870,11 @@
         <v>7621</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5845,13 +5883,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I140" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5865,26 +5903,26 @@
         <v>7614</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5898,11 +5936,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5911,7 +5949,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c t="s" r="I142" s="7">
         <v>43</v>
@@ -5950,7 +5988,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5962,7 +6000,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>104</v>
@@ -5970,7 +6008,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -5985,7 +6023,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6000,7 +6038,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6018,7 +6056,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6030,10 +6068,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6051,7 +6089,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6063,10 +6101,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6084,7 +6122,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6096,10 +6134,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6117,7 +6155,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6129,7 +6167,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>38</v>
@@ -6150,7 +6188,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6183,7 +6221,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6195,10 +6233,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6231,7 +6269,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6240,17 +6278,19 @@
         <v>47</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
-      <c r="M153" s="7"/>
+      <c t="s" r="M153" s="7">
+        <v>119</v>
+      </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
       <c t="s" r="A154" s="6">
@@ -6264,13 +6304,13 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H154" s="8">
         <v>47</v>
@@ -6279,7 +6319,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6297,7 +6337,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6309,10 +6349,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6330,7 +6370,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6339,10 +6379,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>109</v>
@@ -6363,19 +6403,19 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>85</v>
@@ -6411,7 +6451,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6420,17 +6460,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
-      <c r="M159" s="7"/>
+      <c t="s" r="M159" s="7">
+        <v>253</v>
+      </c>
     </row>
     <row r="160" ht="15" customHeight="1">
       <c t="s" r="A160" s="6">
@@ -6444,22 +6486,22 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G160" s="8">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="H160" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6477,7 +6519,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6486,10 +6528,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>41</v>
@@ -6510,22 +6552,22 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6558,13 +6600,13 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>16</v>
@@ -6573,14 +6615,14 @@
         <v>104</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c t="s" r="K164" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -6595,7 +6637,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6607,10 +6649,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6628,7 +6670,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6640,10 +6682,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6661,7 +6703,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6670,13 +6712,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6694,22 +6736,22 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6735,14 +6777,14 @@
         <v>13</v>
       </c>
       <c r="B170" s="7">
-        <v>929</v>
+        <v>463</v>
       </c>
       <c t="s" r="C170" s="7">
         <v>14</v>
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6751,13 +6793,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>263</v>
+        <v>185</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>34</v>
+        <v>267</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6768,29 +6810,29 @@
         <v>13</v>
       </c>
       <c r="B171" s="7">
-        <v>928</v>
+        <v>464</v>
       </c>
       <c t="s" r="C171" s="7">
         <v>14</v>
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>202</v>
+        <v>34</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6801,14 +6843,14 @@
         <v>13</v>
       </c>
       <c r="B172" s="7">
-        <v>781</v>
+        <v>405</v>
       </c>
       <c t="s" r="C172" s="7">
         <v>14</v>
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6817,50 +6859,46 @@
         <v>47</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>264</v>
-      </c>
-      <c t="s" r="K172" s="7">
-        <v>158</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K172" s="7"/>
       <c r="L172" s="7"/>
-      <c t="s" r="M172" s="7">
-        <v>217</v>
-      </c>
+      <c r="M172" s="7"/>
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c t="s" r="A173" s="6">
         <v>13</v>
       </c>
       <c r="B173" s="7">
-        <v>834</v>
+        <v>406</v>
       </c>
       <c t="s" r="C173" s="7">
         <v>14</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6893,7 +6931,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6902,10 +6940,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>71</v>
@@ -6913,7 +6951,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -6928,26 +6966,28 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
-      <c r="M176" s="7"/>
+      <c t="s" r="M176" s="7">
+        <v>273</v>
+      </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c t="s" r="A177" s="6">
@@ -6961,7 +7001,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6973,7 +7013,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J177" s="7">
         <v>34</v>
@@ -6994,7 +7034,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7006,10 +7046,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7027,7 +7067,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7042,7 +7082,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7060,7 +7100,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7072,10 +7112,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7093,7 +7133,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7102,13 +7142,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7126,22 +7166,22 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7174,7 +7214,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7186,10 +7226,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7207,7 +7247,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7216,13 +7256,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7240,13 +7280,13 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>47</v>
@@ -7255,7 +7295,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7288,7 +7328,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7303,7 +7343,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7321,7 +7361,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7333,10 +7373,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7354,7 +7394,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7369,7 +7409,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7387,7 +7427,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7402,7 +7442,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7420,7 +7460,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7429,13 +7469,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7453,22 +7493,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
+        <v>280</v>
+      </c>
+      <c r="F193" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G193" s="8">
+        <v>163</v>
+      </c>
+      <c t="s" r="H193" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I193" s="7">
+        <v>161</v>
+      </c>
+      <c t="s" r="J193" s="7">
         <v>275</v>
-      </c>
-      <c r="F193" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G193" s="8">
-        <v>161</v>
-      </c>
-      <c t="s" r="H193" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I193" s="7">
-        <v>159</v>
-      </c>
-      <c t="s" r="J193" s="7">
-        <v>269</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7501,7 +7541,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7513,10 +7553,10 @@
         <v>90</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7534,7 +7574,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7546,10 +7586,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7567,7 +7607,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7576,13 +7616,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7600,22 +7640,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7648,7 +7688,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7657,18 +7697,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -7683,13 +7723,13 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>16</v>
@@ -7716,7 +7756,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7728,10 +7768,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7749,7 +7789,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7764,7 +7804,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7782,7 +7822,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7794,10 +7834,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7815,7 +7855,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7824,13 +7864,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7848,22 +7888,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7881,7 +7921,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7893,10 +7933,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7929,7 +7969,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7938,13 +7978,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="I209" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7962,13 +8002,13 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>16</v>
@@ -7977,7 +8017,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7995,7 +8035,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8004,13 +8044,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8028,19 +8068,19 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>24</v>
@@ -8061,7 +8101,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8070,13 +8110,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8109,7 +8149,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8118,13 +8158,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>262</v>
+        <v>303</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8142,19 +8182,19 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>262</v>
+        <v>303</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>36</v>
@@ -8175,7 +8215,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8190,14 +8230,14 @@
         <v>53</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="K217" s="7">
         <v>52</v>
       </c>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8227,7 +8267,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8236,18 +8276,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I219" s="7">
         <v>99</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8262,13 +8302,13 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>16</v>
@@ -8277,7 +8317,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8295,7 +8335,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8307,10 +8347,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8328,7 +8368,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8343,7 +8383,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8361,7 +8401,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8373,10 +8413,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="K223" s="7">
         <v>93</v>
@@ -8398,7 +8438,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8413,10 +8453,10 @@
         <v>66</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c t="s" r="K224" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
@@ -8435,7 +8475,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8444,20 +8484,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I225" s="7">
         <v>111</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8472,29 +8512,29 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="K226" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -8524,13 +8564,13 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>47</v>
@@ -8539,12 +8579,12 @@
         <v>104</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -8559,7 +8599,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8568,13 +8608,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8592,29 +8632,29 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c t="s" r="K230" s="7">
         <v>21</v>
       </c>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -8629,7 +8669,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8662,7 +8702,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8674,7 +8714,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>96</v>
@@ -8710,7 +8750,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8722,7 +8762,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>92</v>
@@ -8743,7 +8783,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8752,7 +8792,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="I235" s="7">
         <v>93</v>
@@ -8776,19 +8816,19 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>26</v>
@@ -8809,7 +8849,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8824,7 +8864,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8857,7 +8897,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8869,14 +8909,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
-      <c r="M239" s="7"/>
+      <c t="s" r="M239" s="7">
+        <v>313</v>
+      </c>
     </row>
     <row r="240" ht="15" customHeight="1">
       <c t="s" r="A240" s="6">
@@ -8890,7 +8932,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8902,10 +8944,10 @@
         <v>103</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8923,7 +8965,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8935,10 +8977,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8956,7 +8998,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8965,13 +9007,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9004,7 +9046,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9013,10 +9055,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>48</v>
@@ -9039,29 +9081,29 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="K245" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9091,7 +9133,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9103,14 +9145,16 @@
         <v>35</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>91</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
-      <c r="M247" s="7"/>
+      <c t="s" r="M247" s="7">
+        <v>318</v>
+      </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
       <c t="s" r="A248" s="6">
@@ -9124,7 +9168,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9136,10 +9180,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9157,7 +9201,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9169,7 +9213,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>49</v>
@@ -9190,7 +9234,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9223,7 +9267,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9232,13 +9276,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9256,13 +9300,13 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>47</v>
@@ -9271,7 +9315,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9289,7 +9333,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9298,13 +9342,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9337,7 +9381,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9349,15 +9393,15 @@
         <v>47</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>318</v>
+        <v>91</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9365,14 +9409,14 @@
         <v>13</v>
       </c>
       <c r="B256" s="7">
-        <v>463</v>
+        <v>929</v>
       </c>
       <c t="s" r="C256" s="7">
         <v>14</v>
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9381,64 +9425,72 @@
         <v>47</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>182</v>
+        <v>325</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>298</v>
-      </c>
-      <c r="K256" s="7"/>
+        <v>34</v>
+      </c>
+      <c t="s" r="K256" s="7">
+        <v>33</v>
+      </c>
       <c r="L256" s="7"/>
-      <c r="M256" s="7"/>
+      <c t="s" r="M256" s="7">
+        <v>230</v>
+      </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
       <c t="s" r="A257" s="6">
         <v>13</v>
       </c>
       <c r="B257" s="7">
-        <v>464</v>
+        <v>928</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>34</v>
+        <v>205</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>295</v>
-      </c>
-      <c r="K257" s="7"/>
+        <v>77</v>
+      </c>
+      <c t="s" r="K257" s="7">
+        <v>93</v>
+      </c>
       <c r="L257" s="7"/>
-      <c r="M257" s="7"/>
+      <c t="s" r="M257" s="7">
+        <v>219</v>
+      </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
       <c t="s" r="A258" s="6">
         <v>13</v>
       </c>
       <c r="B258" s="7">
-        <v>405</v>
+        <v>781</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9447,46 +9499,50 @@
         <v>47</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>37</v>
-      </c>
-      <c r="K258" s="7"/>
+        <v>285</v>
+      </c>
+      <c t="s" r="K258" s="7">
+        <v>160</v>
+      </c>
       <c r="L258" s="7"/>
-      <c r="M258" s="7"/>
+      <c t="s" r="M258" s="7">
+        <v>220</v>
+      </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
       <c t="s" r="A259" s="6">
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>406</v>
+        <v>834</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>274</v>
+        <v>97</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9519,22 +9575,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9552,16 +9608,16 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I262" s="7">
         <v>21</v>
@@ -9585,22 +9641,22 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9618,16 +9674,16 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>37</v>
@@ -9651,22 +9707,22 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9684,7 +9740,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9696,10 +9752,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9732,13 +9788,13 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>16</v>
@@ -9747,7 +9803,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9765,7 +9821,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9774,13 +9830,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="I269" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9798,19 +9854,19 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>111</v>
@@ -9831,7 +9887,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9846,7 +9902,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9879,7 +9935,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9888,18 +9944,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -9914,13 +9970,13 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>16</v>
@@ -9933,7 +9989,9 @@
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
-      <c r="M274" s="7"/>
+      <c t="s" r="M274" s="7">
+        <v>334</v>
+      </c>
     </row>
     <row r="275" ht="15" customHeight="1">
       <c t="s" r="A275" s="6">
@@ -9947,7 +10005,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9956,13 +10014,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I275" s="7">
         <v>118</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9980,22 +10038,22 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10013,7 +10071,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -10022,13 +10080,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>34</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10046,13 +10104,13 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>47</v>
@@ -10083,7 +10141,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10095,10 +10153,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10131,7 +10189,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10140,10 +10198,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>100</v>
@@ -10166,13 +10224,13 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>47</v>
@@ -10181,7 +10239,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10199,7 +10257,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10208,13 +10266,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10232,22 +10290,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10265,7 +10323,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10274,10 +10332,10 @@
         <v>47</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>109</v>
@@ -10298,22 +10356,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10346,22 +10404,22 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10379,7 +10437,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10391,7 +10449,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>36</v>
@@ -10412,7 +10470,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10424,10 +10482,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10445,7 +10503,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10454,13 +10512,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10493,19 +10551,19 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c t="s" r="J293" s="7">
         <v>92</v>
@@ -10526,22 +10584,22 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10559,19 +10617,19 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>87</v>
@@ -10592,22 +10650,22 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="I296" s="7">
+        <v>345</v>
+      </c>
+      <c t="s" r="J296" s="7">
         <v>337</v>
-      </c>
-      <c t="s" r="J296" s="7">
-        <v>329</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10640,7 +10698,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10649,13 +10707,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10673,13 +10731,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>16</v>
@@ -10688,7 +10746,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10706,7 +10764,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10715,13 +10773,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10739,19 +10797,19 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>87</v>
@@ -10787,13 +10845,13 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>16</v>
@@ -10807,7 +10865,7 @@
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -10822,7 +10880,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10831,17 +10889,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>118</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
-      <c r="M304" s="7"/>
+      <c t="s" r="M304" s="7">
+        <v>350</v>
+      </c>
     </row>
     <row r="305" ht="15" customHeight="1">
       <c t="s" r="A305" s="6">
@@ -10855,22 +10915,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I305" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10888,22 +10948,22 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10921,22 +10981,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10954,22 +11014,22 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10987,22 +11047,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11035,7 +11095,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11044,10 +11104,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>104</v>
@@ -11055,7 +11115,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11070,22 +11130,22 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11103,7 +11163,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11112,10 +11172,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>34</v>
@@ -11136,22 +11196,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11169,7 +11229,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11178,13 +11238,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11202,19 +11262,19 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>88</v>
@@ -11250,7 +11310,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11259,13 +11319,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11279,26 +11339,26 @@
         <v>8520</v>
       </c>
       <c t="s" r="C319" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11312,26 +11372,26 @@
         <v>8521</v>
       </c>
       <c t="s" r="C320" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11349,16 +11409,16 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>56</v>
@@ -11397,7 +11457,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11406,17 +11466,19 @@
         <v>47</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>118</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
-      <c r="M323" s="7"/>
+      <c t="s" r="M323" s="7">
+        <v>318</v>
+      </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
       <c t="s" r="A324" s="6">
@@ -11430,13 +11492,13 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>47</v>
@@ -11445,7 +11507,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11463,7 +11525,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11472,13 +11534,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11496,13 +11558,13 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>47</v>
@@ -11529,7 +11591,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11541,7 +11603,7 @@
         <v>39</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>43</v>
@@ -11562,7 +11624,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11574,10 +11636,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11610,7 +11672,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11622,17 +11684,17 @@
         <v>47</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="K330" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -11647,7 +11709,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11659,17 +11721,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>36</v>
       </c>
       <c t="s" r="K331" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -11684,7 +11746,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11693,13 +11755,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="I332" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11717,13 +11779,13 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="H333" s="8">
         <v>16</v>
@@ -11732,7 +11794,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11750,7 +11812,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11762,10 +11824,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11783,7 +11845,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11795,7 +11857,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>60</v>
@@ -11831,7 +11893,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11846,7 +11908,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11864,7 +11926,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11873,10 +11935,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>75</v>
@@ -11897,13 +11959,13 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>16</v>
@@ -11912,7 +11974,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11930,7 +11992,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11939,7 +12001,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>54</v>
@@ -11963,13 +12025,13 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>16</v>
@@ -11978,7 +12040,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12011,7 +12073,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12020,18 +12082,18 @@
         <v>47</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>363</v>
+        <v>372</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12046,22 +12108,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12079,7 +12141,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12088,13 +12150,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12112,22 +12174,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12160,22 +12222,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12193,22 +12255,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="F349" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12226,22 +12288,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c t="s" r="I350" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12259,22 +12321,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12292,22 +12354,22 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12340,27 +12402,27 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>47</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>372</v>
+        <v>186</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -12375,7 +12437,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12384,13 +12446,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12408,13 +12470,13 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>47</v>
@@ -12423,7 +12485,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12441,7 +12503,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12450,7 +12512,7 @@
         <v>47</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>65</v>
@@ -12474,13 +12536,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>47</v>
@@ -12489,7 +12551,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12507,7 +12569,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12516,13 +12578,13 @@
         <v>47</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12555,13 +12617,13 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>20</v>
@@ -12574,7 +12636,9 @@
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
-      <c r="M361" s="7"/>
+      <c t="s" r="M361" s="7">
+        <v>153</v>
+      </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
       <c t="s" r="A362" s="6">
@@ -12588,7 +12652,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12597,13 +12661,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I362" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12621,19 +12685,19 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>81</v>
@@ -12654,7 +12718,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12663,13 +12727,13 @@
         <v>72</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I364" s="7">
         <v>109</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12683,26 +12747,26 @@
         <v>8020</v>
       </c>
       <c t="s" r="C365" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12716,26 +12780,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C366" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12768,7 +12832,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12780,14 +12844,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
-      <c r="M368" s="7"/>
+      <c t="s" r="M368" s="7">
+        <v>193</v>
+      </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
       <c t="s" r="A369" s="6">
@@ -12801,7 +12867,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12810,13 +12876,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="I369" s="7">
         <v>64</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12834,22 +12900,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12867,7 +12933,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12879,10 +12945,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12900,7 +12966,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12909,13 +12975,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12933,22 +12999,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12981,7 +13047,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13014,7 +13080,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13026,7 +13092,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>34</v>
@@ -13047,7 +13113,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13062,7 +13128,7 @@
         <v>93</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13080,7 +13146,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13113,7 +13179,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13122,13 +13188,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13146,22 +13212,22 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13194,7 +13260,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13213,7 +13279,9 @@
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
-      <c r="M382" s="7"/>
+      <c t="s" r="M382" s="7">
+        <v>393</v>
+      </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
       <c t="s" r="A383" s="6">
@@ -13227,7 +13295,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13239,10 +13307,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13260,7 +13328,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13272,10 +13340,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13304,11 +13372,11 @@
         <v>664</v>
       </c>
       <c t="s" r="C386" s="7">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F386" s="7">
         <v>330</v>
@@ -13317,13 +13385,13 @@
         <v>20</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13341,22 +13409,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F387" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13374,25 +13442,25 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F388" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="K388" s="7">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
@@ -13426,7 +13494,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="F390" s="7">
         <v>330</v>
@@ -13435,13 +13503,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13459,22 +13527,22 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="F391" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13507,7 +13575,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
@@ -13516,10 +13584,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>96</v>
@@ -13540,22 +13608,22 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="F394" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13588,7 +13656,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
@@ -13597,10 +13665,10 @@
         <v>20</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>19</v>
@@ -13621,16 +13689,16 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F397" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c t="s" r="I397" s="7">
         <v>21</v>
@@ -13654,22 +13722,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13702,16 +13770,16 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c t="s" r="I400" s="7">
         <v>57</v>
@@ -13735,22 +13803,22 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13783,13 +13851,13 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>16</v>
@@ -13798,11 +13866,13 @@
         <v>64</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
-      <c r="M403" s="7"/>
+      <c t="s" r="M403" s="7">
+        <v>409</v>
+      </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
       <c t="s" r="A404" s="6">
@@ -13816,7 +13886,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -13825,7 +13895,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c t="s" r="I404" s="7">
         <v>67</v>
@@ -13839,7 +13909,7 @@
     </row>
     <row r="405" ht="16.5" customHeight="1">
       <c t="s" r="A405" s="9">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B405" s="9"/>
       <c r="C405" s="9"/>
@@ -13859,7 +13929,7 @@
     <row r="406" ht="65.25" customHeight="1"/>
     <row r="407" ht="16.5" customHeight="1">
       <c t="s" r="A407" s="10">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="B407" s="10"/>
       <c r="C407" s="10"/>
@@ -13872,7 +13942,7 @@
       <c r="J407" s="10"/>
       <c r="K407" s="10"/>
       <c t="s" r="L407" s="11">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="M407" s="11"/>
       <c r="N407" s="11"/>
